--- a/testAutomation_v1.0/test/Manual/C1App/FOC/ebookAccessibilityTest_thor_details.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/FOC/ebookAccessibilityTest_thor_details.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30516"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0E802F6-4659-422C-B2EA-469425EBE063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{552FAFCF-E59A-4266-B80E-8C9FCA043213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Register" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="371">
   <si>
     <t>eBook Accessibility — Keyboard-Only Usability Register.  PURPOSE OF TEST EXECUTION: verify the Cambridge One eBook reader can be used with a keyboard alone (no mouse) for accessibility / screen-reader support — that every in-page interactive item (Note marker, Hotlink) and every reader toolbar control can be reached with Tab / Shift+Tab and operated with Enter, in a sensible order.  One student login covers all 35 cases in a single session: S1 = in-page focus (19), S2 = toolbar focus (16).</t>
   </si>
@@ -42,7 +42,10 @@
     <t>S.No.</t>
   </si>
   <si>
-    <t>Test Case ID</t>
+    <t>ATCID</t>
+  </si>
+  <si>
+    <t>MTC ID</t>
   </si>
   <si>
     <t>Title</t>
@@ -79,6 +82,9 @@
   </si>
   <si>
     <t>Comments / Defect ID</t>
+  </si>
+  <si>
+    <t>TST_KBOA_TC_1</t>
   </si>
   <si>
     <t>S1-TC1</t>
@@ -124,6 +130,9 @@
     <t/>
   </si>
   <si>
+    <t>TST_KBOA_TC_2</t>
+  </si>
+  <si>
     <t>S1-TC2</t>
   </si>
   <si>
@@ -148,6 +157,9 @@
     <t>With focus on the reader content, one press of Tab moved the focus indicator onto the Note icon on page 22 (focus ring visible), confirming the Note is the first keyboard-reachable interactive element on the page.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_3</t>
+  </si>
+  <si>
     <t>S1-TC3</t>
   </si>
   <si>
@@ -166,6 +178,9 @@
     <t>From the focused Note, a second Tab carried focus past the page content and onto the toolbar Home button (focus ring appeared on Home), showing the tab path correctly leaves the page and enters the toolbar.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_4</t>
+  </si>
+  <si>
     <t>S1-TC4</t>
   </si>
   <si>
@@ -187,6 +202,9 @@
     <t>Pressing Shift+Tab from Home moved focus backwards and it landed again on the Note icon on page 22 (focus ring returned to the Note), confirming focus moves in both directions across the page boundary.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_5</t>
+  </si>
+  <si>
     <t>S1-TC5</t>
   </si>
   <si>
@@ -208,6 +226,9 @@
     <t>With the Note icon focused, pressing Enter activated it and the "My notes" side panel opened at the side of the reader, its heading visible on screen — the activation worked entirely from the keyboard.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_6</t>
+  </si>
+  <si>
     <t>S1-TC6</t>
   </si>
   <si>
@@ -224,6 +245,9 @@
   </si>
   <si>
     <t>Moving focus to the panel close control and pressing Enter dismissed the "My notes" panel; its heading disappeared and the reader returned to the full page view, confirming the panel closes by keyboard.</t>
+  </si>
+  <si>
+    <t>TST_KBOA_TC_7</t>
   </si>
   <si>
     <t>S1-TC7</t>
@@ -251,6 +275,9 @@
     <t>Navigated to page 24 via the page-number control. The page displayed its single "Go to page" Hotlink icon, and clicking into the reading area placed focus at the start of the content, ready to traverse to the Hotlink.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_8</t>
+  </si>
+  <si>
     <t>S1-TC8</t>
   </si>
   <si>
@@ -266,6 +293,9 @@
     <t>One Tab press from the reading area moved focus onto the Hotlink icon on page 24 (focus ring visible), confirming the Hotlink is keyboard-reachable as the interactive element on the page.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_9</t>
+  </si>
+  <si>
     <t>S1-TC9</t>
   </si>
   <si>
@@ -281,6 +311,9 @@
     <t>A further Tab moved focus from the Hotlink out of the page content and onto the toolbar Home button, showing the tab path exits the page to the toolbar after the single in-page item.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_10</t>
+  </si>
+  <si>
     <t>S1-TC10</t>
   </si>
   <si>
@@ -296,6 +329,9 @@
     <t>Shift+Tab from Home returned focus in reverse onto the Hotlink icon on page 24 (focus ring back on the Hotlink), again confirming bidirectional traversal across the page/toolbar boundary.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_11</t>
+  </si>
+  <si>
     <t>S1-TC11</t>
   </si>
   <si>
@@ -317,6 +353,9 @@
     <t>Pressing Enter on the focused Hotlink followed its link: the reader jumped and the page-number readout updated to page 28, the link target. The link activated by keyboard and navigated as intended.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_12</t>
+  </si>
+  <si>
     <t>S1-TC12</t>
   </si>
   <si>
@@ -339,6 +378,9 @@
   </si>
   <si>
     <t>Used the page-number control to return the reader to page 24, leaving the Hotlink flow in a clean, known state for the cases that follow. No errors observed.</t>
+  </si>
+  <si>
+    <t>TST_KBOA_TC_13</t>
   </si>
   <si>
     <t>S1-TC13</t>
@@ -364,6 +406,9 @@
     <t>Navigated to page 26, which contains no Note and no Hotlink. The page displayed as plain content and focus was placed at the start of the reading area — the correct baseline for the no-hotspot check that follows.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_14</t>
+  </si>
+  <si>
     <t>S1-TC14</t>
   </si>
   <si>
@@ -377,6 +422,9 @@
   </si>
   <si>
     <t>Pressing Tab on the non-interactive page 26 skipped straight over the content and landed directly on the toolbar Home button — nothing in the page caught focus. This confirms keyboard focus is not trapped on plain page content.</t>
+  </si>
+  <si>
+    <t>TST_KBOA_TC_15</t>
   </si>
   <si>
     <t>S1-TC15</t>
@@ -406,6 +454,9 @@
     <t>Navigated to page 28, which carries both a Note icon and a Hotlink icon; both were visible on the page and focus was placed at the start of the reading area — the baseline for the multi-item tab-order checks.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_16</t>
+  </si>
+  <si>
     <t>S1-TC16</t>
   </si>
   <si>
@@ -421,6 +472,9 @@
     <t>The first Tab on page 28 moved focus onto the Note icon first (focus ring on the Note), establishing the correct reading order before the Hotlink.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_17</t>
+  </si>
+  <si>
     <t>S1-TC17</t>
   </si>
   <si>
@@ -436,6 +490,9 @@
     <t>The next Tab advanced focus from the Note to the Hotlink icon on the same page (focus ring moved to the Hotlink), confirming the two in-page items are reached in the expected Note-then-Hotlink sequence.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_18</t>
+  </si>
+  <si>
     <t>S1-TC18</t>
   </si>
   <si>
@@ -451,6 +508,9 @@
     <t>The following Tab moved focus from the Hotlink out to the toolbar Home button. Across the three presses the observed order was Note then Hotlink then Home, matching the intended keyboard reading order for a page holding both items.</t>
   </si>
   <si>
+    <t>TST_KBOA_TC_19</t>
+  </si>
+  <si>
     <t>S1-TC19</t>
   </si>
   <si>
@@ -472,6 +532,9 @@
     <t>Navigated the reader back to page 20 to park it on a neutral page before the toolbar suite begins. No errors observed.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_1</t>
+  </si>
+  <si>
     <t>S2-TC1</t>
   </si>
   <si>
@@ -490,6 +553,9 @@
     <t>From the shared session (reader last left on page 20) navigated to page 26 and clicked into the reading area, giving a consistent keyboard start point for the toolbar traversal. No re-login was needed — the same signed-in reader session was reused.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_2</t>
+  </si>
+  <si>
     <t>S2-TC2</t>
   </si>
   <si>
@@ -505,6 +571,9 @@
     <t>The first Tab from the reading area landed focus on the toolbar Home button (focus ring on Home) — the expected start of the toolbar walk.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_3</t>
+  </si>
+  <si>
     <t>S2-TC3</t>
   </si>
   <si>
@@ -520,6 +589,9 @@
     <t>The next Tab advanced focus to the Content button on the toolbar (focus ring on Content), so a keyboard-only user can reach it.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_4</t>
+  </si>
+  <si>
     <t>S2-TC4</t>
   </si>
   <si>
@@ -535,6 +607,9 @@
     <t>Tab moved focus on to the Tools button (focus ring on Tools), keeping the left-to-right toolbar order intact.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_5</t>
+  </si>
+  <si>
     <t>S2-TC5</t>
   </si>
   <si>
@@ -550,6 +625,9 @@
     <t>Tab advanced focus to the Zoom Out button (focus ring on Zoom Out), the first of the zoom controls reached in sequence.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_6</t>
+  </si>
+  <si>
     <t>S2-TC6</t>
   </si>
   <si>
@@ -565,6 +643,9 @@
     <t>Tab advanced focus to the Zoom In button (focus ring on Zoom In), immediately after Zoom Out.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_7</t>
+  </si>
+  <si>
     <t>S2-TC7</t>
   </si>
   <si>
@@ -580,6 +661,9 @@
     <t>Tab advanced focus to the Fit To Height button (focus ring on it), following the zoom controls.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_8</t>
+  </si>
+  <si>
     <t>S2-TC8</t>
   </si>
   <si>
@@ -595,6 +679,9 @@
     <t>Tab advanced focus to the Jump to Page (page-number) control (focus ring on it). Focusing it surfaced its page-entry pop-up, which the next case dismisses.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_9</t>
+  </si>
+  <si>
     <t>S2-TC9</t>
   </si>
   <si>
@@ -613,6 +700,9 @@
     <t>Dismissed the page-number pop-up that Jump to Page had opened, then pressed Tab; focus moved past it onto the Previous (previous-page) button, confirming a lingering pop-up does not block the keyboard path.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_10</t>
+  </si>
+  <si>
     <t>S2-TC10</t>
   </si>
   <si>
@@ -628,6 +718,9 @@
     <t>Tab advanced focus to the Table of Contents button (focus ring on it), so a keyboard user can reach the contents from the toolbar.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_11</t>
+  </si>
+  <si>
     <t>S2-TC11</t>
   </si>
   <si>
@@ -643,6 +736,9 @@
     <t>Tab advanced focus to the Next (next-page) button (focus ring on Next).</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_12</t>
+  </si>
+  <si>
     <t>S2-TC12</t>
   </si>
   <si>
@@ -658,6 +754,9 @@
     <t>Tab advanced focus to the Single Page View toggle (focus ring on it), confirming the layout control is keyboard-reachable.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_13</t>
+  </si>
+  <si>
     <t>S2-TC13</t>
   </si>
   <si>
@@ -673,6 +772,9 @@
     <t>Tab advanced focus to the Change Course Material button (focus ring on it), a peripheral but still reachable toolbar control.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_14</t>
+  </si>
+  <si>
     <t>S2-TC14</t>
   </si>
   <si>
@@ -688,6 +790,9 @@
     <t>Tab advanced focus to the Move Toolbar button (focus ring on it); the control is keyboard-reachable even though it is used rarely.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_15</t>
+  </si>
+  <si>
     <t>S2-TC15</t>
   </si>
   <si>
@@ -703,6 +808,9 @@
     <t>Tab advanced focus to the Toolbar Status control (focus ring on it) — the last control in the toolbar walk; every toolbar item proved keyboard-reachable in order.</t>
   </si>
   <si>
+    <t>TST_EBTF_TC_16</t>
+  </si>
+  <si>
     <t>S2-TC16</t>
   </si>
   <si>
@@ -719,6 +827,9 @@
   </si>
   <si>
     <t>Suite ID</t>
+  </si>
+  <si>
+    <t>ATC ID</t>
   </si>
   <si>
     <t>Test Suite</t>
@@ -1066,7 +1177,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1086,8 +1197,16 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1110,6 +1229,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1123,7 +1248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1143,13 +1268,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1491,61 +1622,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr defaultColWidth="22.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13" style="6" customWidth="1"/>
-    <col min="3" max="3" width="42" style="6" customWidth="1"/>
-    <col min="4" max="4" width="40" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10" style="6" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="6"/>
-    <col min="7" max="7" width="42" style="6" customWidth="1"/>
-    <col min="8" max="8" width="50" style="6" customWidth="1"/>
-    <col min="9" max="9" width="26" style="6" customWidth="1"/>
-    <col min="10" max="10" width="46" style="6" customWidth="1"/>
-    <col min="11" max="11" width="38" style="6" customWidth="1"/>
-    <col min="12" max="12" width="52" style="6" customWidth="1"/>
-    <col min="13" max="13" width="10" style="6" customWidth="1"/>
-    <col min="14" max="14" width="24" style="6" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="16384" width="22.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:15" ht="30" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-    </row>
-    <row r="2" spans="1:14" ht="21" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" ht="21" customHeight="1">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1588,1550 +1707,1658 @@
       <c r="N3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="76.5">
+      <c r="O3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="183">
       <c r="A4" s="2">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="152.25">
       <c r="A5" s="2">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="60.75">
+    </row>
+    <row r="6" spans="1:15" ht="152.25">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="137.25">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="152.25">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="137.25">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="152.25">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="137.25">
       <c r="A11" s="2">
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="121.5">
       <c r="A12" s="2">
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="137.25">
       <c r="A13" s="2">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="152.25">
       <c r="A14" s="2">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="106.5">
       <c r="A15" s="2">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="152.25">
       <c r="A16" s="2">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>105</v>
+        <v>26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="76.5">
+        <v>28</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="167.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="152.25">
       <c r="A18" s="2">
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="106.5">
       <c r="A19" s="2">
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="137.25">
       <c r="A20" s="2">
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>142</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>39</v>
+        <v>143</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="76.5">
+        <v>28</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="167.25">
       <c r="A21" s="2">
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="91.5">
       <c r="A22" s="2">
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>158</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="76.5">
+        <v>28</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="167.25">
       <c r="A23" s="2">
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>143</v>
+        <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>165</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="106.5">
       <c r="A24" s="2">
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="91.5">
       <c r="A25" s="2">
         <v>22</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>154</v>
+        <v>36</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>26</v>
+        <v>178</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="76.5">
       <c r="A26" s="2">
         <v>23</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="91.5">
       <c r="A27" s="2">
         <v>24</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>165</v>
+        <v>26</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="76.5">
       <c r="A28" s="2">
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>32</v>
+        <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>169</v>
+        <v>36</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>195</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="76.5">
       <c r="A29" s="2">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>174</v>
+        <v>36</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>175</v>
+        <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="106.5">
       <c r="A30" s="2">
         <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>142</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>178</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>32</v>
+        <v>206</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>179</v>
+        <v>36</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="60.75">
+        <v>28</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="152.25">
       <c r="A31" s="2">
         <v>28</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>185</v>
+        <v>36</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>26</v>
+        <v>215</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="91.5">
       <c r="A32" s="2">
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>142</v>
+        <v>218</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>189</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>220</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>191</v>
+        <v>26</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>26</v>
+        <v>221</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="76.5">
       <c r="A33" s="2">
         <v>30</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>142</v>
+        <v>224</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>32</v>
+        <v>225</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>195</v>
+        <v>36</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>226</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>26</v>
+        <v>227</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="91.5">
       <c r="A34" s="2">
         <v>31</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>232</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>201</v>
+        <v>26</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>26</v>
+        <v>233</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="91.5">
       <c r="A35" s="2">
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>202</v>
+        <v>234</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>142</v>
+        <v>236</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>32</v>
+        <v>237</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>205</v>
+        <v>36</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>206</v>
+        <v>26</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>26</v>
+        <v>239</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="91.5">
       <c r="A36" s="2">
         <v>33</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>142</v>
+        <v>242</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>209</v>
+        <v>106</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>32</v>
+        <v>243</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>211</v>
+        <v>26</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>26</v>
+        <v>245</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="121.5">
       <c r="A37" s="2">
         <v>34</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>142</v>
+        <v>248</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>32</v>
+        <v>249</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>215</v>
+        <v>36</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>216</v>
+        <v>26</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>26</v>
+        <v>251</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="45.75">
+        <v>28</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="121.5">
       <c r="A38" s="2">
         <v>35</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>217</v>
+        <v>252</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>134</v>
+        <v>253</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>218</v>
+        <v>106</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>137</v>
+        <v>255</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>220</v>
+        <v>157</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>221</v>
+        <v>26</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -3140,843 +3367,943 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
-    <col min="7" max="7" width="52" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr defaultColWidth="15.140625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="91.5">
+      <c r="A2" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="45.75">
+      <c r="A3" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="91.5">
+      <c r="A4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60.75">
+      <c r="A5" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60.75">
+      <c r="A6" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="60.75">
+      <c r="A7" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="60.75">
+      <c r="A8" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="45.75">
+      <c r="A9" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="60.75">
+      <c r="A10" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="60.75">
+      <c r="A11" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="60.75">
+      <c r="A12" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="60.75">
+      <c r="A13" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="76.5">
+      <c r="A14" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="76.5">
+      <c r="A15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="60.75">
+      <c r="A16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="76.5">
+      <c r="A17" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="45.75">
+      <c r="A18" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="106.5">
+      <c r="A19" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="76.5">
+      <c r="A20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="76.5">
+      <c r="A21" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="60.75">
+      <c r="A22" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="60.75">
+      <c r="A23" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="60.75">
+      <c r="A24" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="60.75">
+      <c r="A25" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="60.75">
+      <c r="A26" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="60.75">
+      <c r="A27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="76.5">
+      <c r="A28" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="76.5">
+      <c r="A29" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="60.75">
+      <c r="A30" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="45.75">
+      <c r="A31" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D31" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="F31" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="32" spans="1:8" ht="60.75">
+      <c r="A32" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="F32" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="33" spans="1:8" ht="60.75">
+      <c r="A33" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="F33" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F7" s="2" t="s">
+    </row>
+    <row r="34" spans="1:8" ht="60.75">
+      <c r="A34" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="F34" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F10" s="2" t="s">
+    </row>
+    <row r="35" spans="1:8" ht="76.5">
+      <c r="A35" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="F35" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F13" s="2" t="s">
+    </row>
+    <row r="36" spans="1:8" ht="76.5">
+      <c r="A36" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D36" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -3987,415 +4314,475 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="52" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
+    <row r="1" spans="1:7" ht="45.75">
+      <c r="A1" s="10" t="s">
+        <v>259</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="4" t="s">
-        <v>15</v>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="45.75">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="5">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30.75">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="5">
+        <v>31</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30.75">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="B4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="5">
+        <v>40</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30.75">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30.75">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30.75">
+      <c r="A7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45.75">
+      <c r="A8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30.75">
+      <c r="A9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30.75">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="5">
+      <c r="F10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30.75">
+      <c r="A11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="5">
+      <c r="F11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30.75">
+      <c r="A12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="5">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="E12" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30.75">
+      <c r="A13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D13" s="5">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="E13" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30.75">
+      <c r="A14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="5">
+        <v>2</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30.75">
+      <c r="A15" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="5">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="E15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="60.75">
+      <c r="A16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30.75">
+      <c r="A17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="5">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="E17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="30.75">
+      <c r="A18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="E18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30.75">
+      <c r="A19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="5">
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="E19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30.75">
+      <c r="A20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="5">
         <v>1</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="5">
-        <v>2</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="5">
-        <v>4</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>319</v>
+        <v>157</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4406,356 +4793,401 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="25.5703125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" style="6" customWidth="1"/>
-    <col min="2" max="2" width="38" style="6" customWidth="1"/>
-    <col min="3" max="3" width="14" style="6" customWidth="1"/>
-    <col min="4" max="4" width="52" style="6" customWidth="1"/>
-    <col min="5" max="5" width="22" style="6" customWidth="1"/>
-    <col min="6" max="6" width="52" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="6"/>
+    <col min="1" max="16384" width="25.5703125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="45.75">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
+    <row r="1" spans="1:7" ht="45.75">
+      <c r="A1" s="11" t="s">
+        <v>259</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>301</v>
+        <v>261</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="30.75">
-      <c r="A2" s="4" t="s">
-        <v>140</v>
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="30.75">
+      <c r="A2" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="5">
+        <v>161</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D2" s="5">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>146</v>
+        <v>117</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30.75">
+      <c r="A3" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C3" s="5">
+        <v>168</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="5">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>151</v>
+        <v>36</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30.75">
+      <c r="A4" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="5">
+        <v>174</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="5">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>156</v>
+        <v>36</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30.75">
+      <c r="A5" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="30.75">
+      <c r="A6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30.75">
+      <c r="A7" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30.75">
+      <c r="A8" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30.75">
+      <c r="A9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30.75">
+      <c r="A10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30.75">
+      <c r="A11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30.75">
+      <c r="A12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="30.75">
+      <c r="A13" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="30.75">
+      <c r="A14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="30.75">
+      <c r="A15" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="30.75">
+      <c r="A16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="30.75">
+      <c r="A17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="5">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30.75">
-      <c r="A10" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>319</v>
+      <c r="G17" s="4" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
